--- a/video_doorbell.xlsx
+++ b/video_doorbell.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brad.parker/projects/SystemSurveyor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCFC9812-9778-4E44-9051-C9C50E866B68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BACCE1FA-B702-A74A-83F8-DEA6B9656D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="197">
   <si>
     <t>Export date: Jun 29, 2026</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Video Doorbell Element Attributes</t>
-  </si>
-  <si>
-    <t>TD52 - All in One Cloud Video Intercom</t>
   </si>
   <si>
     <t>Name</t>
@@ -87,9 +84,6 @@
   </si>
   <si>
     <t>Device Price</t>
-  </si>
-  <si>
-    <t>1599</t>
   </si>
   <si>
     <t>Installation Hours</t>
@@ -191,19 +185,10 @@
     <t>Link 2 Description</t>
   </si>
   <si>
-    <t>TD52 Product Datasheet</t>
-  </si>
-  <si>
     <t>Link 2 Url</t>
   </si>
   <si>
-    <t>https://docs.verkada.com/docs/td52-overview.pdf</t>
-  </si>
-  <si>
     <t>Accessory 1</t>
-  </si>
-  <si>
-    <t>1-year TD52 License</t>
   </si>
   <si>
     <t>Accessory 2</t>
@@ -263,25 +248,16 @@
     <t>Accessory2</t>
   </si>
   <si>
-    <t>3-year TD52 License</t>
-  </si>
-  <si>
     <t>LIC-TD-3YR</t>
   </si>
   <si>
     <t>Accessory3</t>
   </si>
   <si>
-    <t>5-year TD52 License</t>
-  </si>
-  <si>
     <t>LIC-TD-5YR</t>
   </si>
   <si>
     <t>Accessory4</t>
-  </si>
-  <si>
-    <t>10-year TD52 License</t>
   </si>
   <si>
     <t>LIC-TD-10YR</t>
@@ -297,9 +273,6 @@
   </si>
   <si>
     <t>Accessory6</t>
-  </si>
-  <si>
-    <t>Intercom Surface Mount</t>
   </si>
   <si>
     <t>ACC-INT-SURF</t>
@@ -324,9 +297,6 @@
   </si>
   <si>
     <t>Accessory9</t>
-  </si>
-  <si>
-    <t>Intercom Angle Mount</t>
   </si>
   <si>
     <t>ACC-INT-ANGLE</t>
@@ -368,12 +338,6 @@
     <t>Accessory14</t>
   </si>
   <si>
-    <t>AD33 Card Reader</t>
-  </si>
-  <si>
-    <t>AD33-HW</t>
-  </si>
-  <si>
     <t>Accessory15</t>
   </si>
   <si>
@@ -398,7 +362,268 @@
     <t>ACCX-TBL-1</t>
   </si>
   <si>
-    <t>TD52</t>
+    <t>Intercom Trim Plate (gen2)</t>
+  </si>
+  <si>
+    <t>ACC-INT-TRIM-1</t>
+  </si>
+  <si>
+    <t>TD52 Angle Mount</t>
+  </si>
+  <si>
+    <t>TD52 Surface Mount</t>
+  </si>
+  <si>
+    <t>1-year Intercom License</t>
+  </si>
+  <si>
+    <t>Intercom Rain Hood (gen2)</t>
+  </si>
+  <si>
+    <t>ACC-INT-HOOD-</t>
+  </si>
+  <si>
+    <t>TD63 Conduit Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-COND-3</t>
+  </si>
+  <si>
+    <t>TD53 Conduit Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-COND-2</t>
+  </si>
+  <si>
+    <t>Accessory17</t>
+  </si>
+  <si>
+    <t>TD63 Angle Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-ANGLE-3</t>
+  </si>
+  <si>
+    <t>Accessory18</t>
+  </si>
+  <si>
+    <t>TD53 Angle Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-ANGLE-2</t>
+  </si>
+  <si>
+    <t>Accessory19</t>
+  </si>
+  <si>
+    <t>TD33 Angle Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-ANGLE-4</t>
+  </si>
+  <si>
+    <t>Accessory20</t>
+  </si>
+  <si>
+    <t>10-year Intercom License</t>
+  </si>
+  <si>
+    <t>Accessory21</t>
+  </si>
+  <si>
+    <t>5-year Intercom License</t>
+  </si>
+  <si>
+    <t>Accessory22</t>
+  </si>
+  <si>
+    <t>3-yearIntercom License</t>
+  </si>
+  <si>
+    <t>Accessory23</t>
+  </si>
+  <si>
+    <t>TD53 Emergency Label Kit</t>
+  </si>
+  <si>
+    <t>ACC-INT-SOS-2</t>
+  </si>
+  <si>
+    <t>Accessory24</t>
+  </si>
+  <si>
+    <t>Intercom Emergency Adapter Plate</t>
+  </si>
+  <si>
+    <t>ACC-INT-PLATE-1</t>
+  </si>
+  <si>
+    <t>Accessory25</t>
+  </si>
+  <si>
+    <t>Square Intercom Conduit Surface Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-TS-COND</t>
+  </si>
+  <si>
+    <t>Accessory26</t>
+  </si>
+  <si>
+    <t>Verkada Security Relay</t>
+  </si>
+  <si>
+    <t>ACC-IOX-RELAY</t>
+  </si>
+  <si>
+    <t>Accessory27</t>
+  </si>
+  <si>
+    <t>TK74 Side Angle Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-TK-ANGLE</t>
+  </si>
+  <si>
+    <t>Accessory28</t>
+  </si>
+  <si>
+    <t>TK74 Conduit Surface Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-TK-COND</t>
+  </si>
+  <si>
+    <t>Accessory29</t>
+  </si>
+  <si>
+    <t>TK74 Up Angle Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-TK-UP</t>
+  </si>
+  <si>
+    <t>Accessory30</t>
+  </si>
+  <si>
+    <t>TK74 Flush Mount</t>
+  </si>
+  <si>
+    <t>ACC-INT-TK-FLUSH</t>
+  </si>
+  <si>
+    <t>Accessory31</t>
+  </si>
+  <si>
+    <t>AF64 Mullion Mount - 2</t>
+  </si>
+  <si>
+    <t>ACC-AF-MUL-2</t>
+  </si>
+  <si>
+    <t>Accessory32</t>
+  </si>
+  <si>
+    <t>1-Year Intercom Tenant License (for 10 tenants), Capacity Increase</t>
+  </si>
+  <si>
+    <t>LIC-ITT-1Y-CAP</t>
+  </si>
+  <si>
+    <t>Accessory33</t>
+  </si>
+  <si>
+    <t>3-Year Intercom Tenant License (for 10 tenants), Capacity Increase</t>
+  </si>
+  <si>
+    <t>LIC-ITT-3Y-CAP</t>
+  </si>
+  <si>
+    <t>Accessory34</t>
+  </si>
+  <si>
+    <t>5-Year Intercom Tenant License (for 10 tenants), Capacity Increase</t>
+  </si>
+  <si>
+    <t>LIC-ITT-5Y-CAP</t>
+  </si>
+  <si>
+    <t>Accessory35</t>
+  </si>
+  <si>
+    <t>10-Year Intercom Tenant License (for 10 tenants), Capacity Increase</t>
+  </si>
+  <si>
+    <t>LIC-ITT-10Y-CAP</t>
+  </si>
+  <si>
+    <t>TD33 - Mullion All in One Cloud Video Intercom</t>
+  </si>
+  <si>
+    <t>TD33</t>
+  </si>
+  <si>
+    <t>Audio - Two Way,Video - from End Point Only,Door Release Relay,Handsfree Speakerphone,Access Control Reader</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>TD33 Product Datasheet</t>
+  </si>
+  <si>
+    <t>https://docs.verkada.com/docs/td33-overview.pdf</t>
+  </si>
+  <si>
+    <t>TD53 - All in One Cloud Video Intercom</t>
+  </si>
+  <si>
+    <t>TD63 - All in One Cloud Video Intercom with Keypad</t>
+  </si>
+  <si>
+    <t>TD53</t>
+  </si>
+  <si>
+    <t>TD63</t>
+  </si>
+  <si>
+    <t>TK74</t>
+  </si>
+  <si>
+    <t>1799</t>
+  </si>
+  <si>
+    <t>Audio - Two Way,Video - from End Point Only,Door Release Relay,Handsfree Speakerphone,Access Control Reader,Access Control Keypad</t>
+  </si>
+  <si>
+    <t>Audio - Two Way,Door Release Relay,Handsfree Speakerphone</t>
+  </si>
+  <si>
+    <t>Verkada TK74 Intercoms Page</t>
+  </si>
+  <si>
+    <t>https://www.verkada.com/intercom/tk74/</t>
+  </si>
+  <si>
+    <t>TD53 Product Datasheet</t>
+  </si>
+  <si>
+    <t>TD63 Product Datasheet</t>
+  </si>
+  <si>
+    <t>TS74 Product Datasheet</t>
+  </si>
+  <si>
+    <t>https://docs.verkada.com/docs/td53-overview.pdf</t>
+  </si>
+  <si>
+    <t>https://docs.verkada.com/docs/td63-overview.pdf</t>
+  </si>
+  <si>
+    <t>https://docs.verkada.com/docs/tk74-touchscreen-intercom-datasheet.pdf</t>
+  </si>
+  <si>
+    <t>TK74 - All in One Touchscreen Intercom</t>
   </si>
 </sst>
 </file>
@@ -602,19 +827,19 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyBorder="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyBorder="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="bold" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -936,7 +1161,7 @@
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="14"/>
@@ -1442,7 +1667,7 @@
     </row>
     <row r="2" spans="3:504" ht="200" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="2"/>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="16" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="14"/>
@@ -1954,11 +2179,17 @@
         <v>4</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+        <v>174</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -2457,18 +2688,24 @@
       <c r="SJ3" s="3"/>
     </row>
     <row r="4" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+        <v>174</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>196</v>
+      </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -2967,1522 +3204,1528 @@
       <c r="SJ4" s="5"/>
     </row>
     <row r="5" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C5" s="17"/>
+      <c r="C5" s="18"/>
       <c r="D5" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="ED5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="ER5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="ES5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="ET5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="EZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="FZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="GZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="HZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="ID5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="II5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="IZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="JZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="KZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="LZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="ME5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="ML5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="MZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="ND5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="NZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="ON5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="OZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="PZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="QZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RK5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RL5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RM5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RN5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RO5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RP5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RQ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RR5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RS5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RT5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RU5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RV5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RW5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RX5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RY5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="RZ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SA5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SB5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SC5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SD5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SE5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SF5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SG5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SH5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SI5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="SJ5" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C6" s="17"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>10</v>
+      </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -4981,16 +5224,22 @@
       <c r="SJ6" s="5"/>
     </row>
     <row r="7" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C7" s="17"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -5489,16 +5738,22 @@
       <c r="SJ7" s="5"/>
     </row>
     <row r="8" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C8" s="17"/>
+      <c r="C8" s="18"/>
       <c r="D8" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+        <v>175</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>184</v>
+      </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -5997,1522 +6252,1528 @@
       <c r="SJ8" s="5"/>
     </row>
     <row r="9" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C9" s="17"/>
+      <c r="C9" s="18"/>
       <c r="D9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ED9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ER9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ES9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ET9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ID9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="II9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ME9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ML9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ND9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ON9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RK9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RL9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RM9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RN9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RO9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RP9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RQ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RR9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RS9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RT9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RU9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RV9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RW9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RX9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RY9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RZ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SA9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SB9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SC9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SD9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SE9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SF9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SG9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SH9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SI9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SJ9" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C10" s="17"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+        <v>16</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1499</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G10" s="5">
+        <v>1999</v>
+      </c>
+      <c r="H10" s="5">
+        <v>3999</v>
+      </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -8011,1517 +8272,1517 @@
       <c r="SJ10" s="5"/>
     </row>
     <row r="11" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C11" s="18"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="DZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ED11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ER11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ES11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ET11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="EZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="FZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="GZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="HZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ID11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="II11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="IZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="JZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="KZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="LZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ME11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ML11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="MZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ND11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="NZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="ON11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="OZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="PZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="QZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RK11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RL11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RM11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RN11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RO11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RP11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RQ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RR11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RS11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RT11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RU11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RV11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RW11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RX11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RY11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="RZ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SA11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SB11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SC11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SD11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SE11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SF11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SG11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SH11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SI11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="SJ11" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C12" s="16" t="s">
-        <v>20</v>
+      <c r="C12" s="17" t="s">
+        <v>18</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
@@ -10025,9 +10286,9 @@
       <c r="SJ12" s="5"/>
     </row>
     <row r="13" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C13" s="17"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
@@ -10531,9 +10792,9 @@
       <c r="SJ13" s="5"/>
     </row>
     <row r="14" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C14" s="17"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
@@ -11037,9 +11298,9 @@
       <c r="SJ14" s="5"/>
     </row>
     <row r="15" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C15" s="18"/>
+      <c r="C15" s="19"/>
       <c r="D15" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
@@ -11543,18 +11804,24 @@
       <c r="SJ15" s="5"/>
     </row>
     <row r="16" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
+      <c r="F16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -12053,14 +12320,22 @@
       <c r="SJ16" s="5"/>
     </row>
     <row r="17" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C17" s="17"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>187</v>
+      </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -12559,9 +12834,9 @@
       <c r="SJ17" s="5"/>
     </row>
     <row r="18" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C18" s="17"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -13065,14 +13340,22 @@
       <c r="SJ18" s="7"/>
     </row>
     <row r="19" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C19" s="17"/>
+      <c r="C19" s="18"/>
       <c r="D19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+        <v>28</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -13571,13 +13854,19 @@
       <c r="SJ19" s="5"/>
     </row>
     <row r="20" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C20" s="17"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
+        <v>29</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>177</v>
+      </c>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
@@ -14077,9 +14366,9 @@
       <c r="SJ20" s="7"/>
     </row>
     <row r="21" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C21" s="17"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -14583,14 +14872,22 @@
       <c r="SJ21" s="5"/>
     </row>
     <row r="22" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C22" s="17"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
+        <v>31</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>177</v>
+      </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -15089,9 +15386,9 @@
       <c r="SJ22" s="7"/>
     </row>
     <row r="23" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C23" s="17"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -15595,14 +15892,22 @@
       <c r="SJ23" s="5"/>
     </row>
     <row r="24" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C24" s="17"/>
+      <c r="C24" s="18"/>
       <c r="D24" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+        <v>33</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>177</v>
+      </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
@@ -16101,9 +16406,9 @@
       <c r="SJ24" s="7"/>
     </row>
     <row r="25" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C25" s="17"/>
+      <c r="C25" s="18"/>
       <c r="D25" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -16607,13 +16912,19 @@
       <c r="SJ25" s="5"/>
     </row>
     <row r="26" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C26" s="17"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
+        <v>35</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>177</v>
+      </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
@@ -17113,13 +17424,15 @@
       <c r="SJ26" s="7"/>
     </row>
     <row r="27" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C27" s="17"/>
+      <c r="C27" s="18"/>
       <c r="D27" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="G27" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -17619,9 +17932,9 @@
       <c r="SJ27" s="5"/>
     </row>
     <row r="28" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C28" s="17"/>
+      <c r="C28" s="18"/>
       <c r="D28" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -18125,9 +18438,9 @@
       <c r="SJ28" s="7"/>
     </row>
     <row r="29" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C29" s="18"/>
+      <c r="C29" s="19"/>
       <c r="D29" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -18631,11 +18944,11 @@
       <c r="SJ29" s="5"/>
     </row>
     <row r="30" spans="3:504" ht="19" x14ac:dyDescent="0.2">
-      <c r="C30" s="16" t="s">
-        <v>41</v>
+      <c r="C30" s="17" t="s">
+        <v>39</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -19139,11 +19452,11 @@
       <c r="SJ30" s="5"/>
     </row>
     <row r="31" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C31" s="16" t="s">
-        <v>43</v>
+      <c r="C31" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -19647,9 +19960,9 @@
       <c r="SJ31" s="5"/>
     </row>
     <row r="32" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C32" s="18"/>
+      <c r="C32" s="19"/>
       <c r="D32" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -20153,11 +20466,11 @@
       <c r="SJ32" s="5"/>
     </row>
     <row r="33" spans="3:504" ht="19" x14ac:dyDescent="0.2">
-      <c r="C33" s="16" t="s">
-        <v>46</v>
+      <c r="C33" s="17" t="s">
+        <v>44</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
@@ -20661,16 +20974,22 @@
       <c r="SJ33" s="9"/>
     </row>
     <row r="34" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C34" s="16"/>
+      <c r="C34" s="17"/>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
+        <v>46</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>188</v>
+      </c>
       <c r="I34" s="10"/>
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
@@ -21169,16 +21488,22 @@
       <c r="SJ34" s="10"/>
     </row>
     <row r="35" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C35" s="17"/>
+      <c r="C35" s="18"/>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+        <v>48</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>189</v>
+      </c>
       <c r="I35" s="10"/>
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
@@ -21677,16 +22002,22 @@
       <c r="SJ35" s="10"/>
     </row>
     <row r="36" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C36" s="17"/>
+      <c r="C36" s="18"/>
       <c r="D36" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
+        <v>178</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>192</v>
+      </c>
       <c r="I36" s="10"/>
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
@@ -22185,16 +22516,22 @@
       <c r="SJ36" s="10"/>
     </row>
     <row r="37" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C37" s="18"/>
+      <c r="C37" s="19"/>
       <c r="D37" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
+        <v>179</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>195</v>
+      </c>
       <c r="I37" s="11"/>
       <c r="J37" s="11"/>
       <c r="K37" s="11"/>
@@ -22693,18 +23030,24 @@
       <c r="SJ37" s="11"/>
     </row>
     <row r="38" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C38" s="16" t="s">
-        <v>46</v>
+      <c r="C38" s="17" t="s">
+        <v>44</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
+        <v>113</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>113</v>
+      </c>
       <c r="I38" s="10"/>
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
@@ -23203,16 +23546,22 @@
       <c r="SJ38" s="10"/>
     </row>
     <row r="39" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C39" s="17"/>
+      <c r="C39" s="18"/>
       <c r="D39" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="F39" s="10"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+        <v>53</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>53</v>
+      </c>
       <c r="I39" s="10"/>
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
@@ -23711,9 +24060,9 @@
       <c r="SJ39" s="10"/>
     </row>
     <row r="40" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C40" s="17"/>
+      <c r="C40" s="18"/>
       <c r="D40" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E40" s="10"/>
       <c r="F40" s="10"/>
@@ -24217,9 +24566,9 @@
       <c r="SJ40" s="10"/>
     </row>
     <row r="41" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C41" s="17"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
@@ -24723,9 +25072,9 @@
       <c r="SJ41" s="10"/>
     </row>
     <row r="42" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C42" s="17"/>
+      <c r="C42" s="18"/>
       <c r="D42" s="4" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
@@ -25229,9 +25578,9 @@
       <c r="SJ42" s="10"/>
     </row>
     <row r="43" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C43" s="17"/>
+      <c r="C43" s="18"/>
       <c r="D43" s="4" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="10"/>
@@ -25735,9 +26084,9 @@
       <c r="SJ43" s="10"/>
     </row>
     <row r="44" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C44" s="17"/>
+      <c r="C44" s="18"/>
       <c r="D44" s="4" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="10"/>
@@ -26241,9 +26590,9 @@
       <c r="SJ44" s="10"/>
     </row>
     <row r="45" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C45" s="17"/>
+      <c r="C45" s="18"/>
       <c r="D45" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
@@ -26747,9 +27096,9 @@
       <c r="SJ45" s="10"/>
     </row>
     <row r="46" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C46" s="17"/>
+      <c r="C46" s="18"/>
       <c r="D46" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E46" s="10"/>
       <c r="F46" s="10"/>
@@ -27253,9 +27602,9 @@
       <c r="SJ46" s="10"/>
     </row>
     <row r="47" spans="3:504" x14ac:dyDescent="0.2">
-      <c r="C47" s="18"/>
+      <c r="C47" s="19"/>
       <c r="D47" s="8" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="11"/>
@@ -27826,7 +28175,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -27839,39 +28188,39 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" t="s">
         <v>67</v>
-      </c>
-      <c r="B1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="E2">
-        <v>249</v>
+        <v>99</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -27879,19 +28228,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="E3">
-        <v>599</v>
+        <v>329</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -27899,19 +28248,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E4">
-        <v>999</v>
+        <v>39</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -27919,19 +28268,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E5">
-        <v>1999</v>
+        <v>1199</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -27939,19 +28288,19 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E6">
-        <v>99</v>
+        <v>999</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -27959,19 +28308,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E7">
-        <v>199</v>
+        <v>599</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -27979,19 +28328,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
         <v>90</v>
       </c>
-      <c r="B8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
       <c r="E8">
-        <v>399</v>
+        <v>249</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -27999,16 +28348,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E9">
         <v>99</v>
@@ -28019,16 +28368,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E10">
         <v>99</v>
@@ -28039,19 +28388,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E11">
-        <v>249</v>
+        <v>399</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -28059,19 +28408,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="E12">
-        <v>599</v>
+        <v>199</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -28079,19 +28428,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="E13">
-        <v>999</v>
+        <v>249</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -28099,19 +28448,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E14">
-        <v>1199</v>
+        <v>99</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -28119,19 +28468,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E15">
-        <v>349</v>
+        <v>49</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -28139,19 +28488,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>12</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E16">
-        <v>39</v>
+        <v>399</v>
       </c>
       <c r="F16">
         <v>0</v>
@@ -28159,21 +28508,401 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="B17" t="s">
         <v>118</v>
       </c>
       <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
         <v>119</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17">
+        <v>399</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>120</v>
       </c>
-      <c r="E17">
-        <v>329</v>
-      </c>
-      <c r="F17">
+      <c r="B18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18">
+        <v>399</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>123</v>
+      </c>
+      <c r="B19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19">
+        <v>399</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>126</v>
+      </c>
+      <c r="B20" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20">
+        <v>199</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21">
+        <v>1999</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>131</v>
+      </c>
+      <c r="B22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22">
+        <v>999</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>133</v>
+      </c>
+      <c r="B23" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23">
+        <v>599</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24">
+        <v>29</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" t="s">
+        <v>140</v>
+      </c>
+      <c r="E25">
+        <v>199</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26">
+        <v>149</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>144</v>
+      </c>
+      <c r="B27" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27">
+        <v>199</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" t="s">
+        <v>148</v>
+      </c>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28">
+        <v>399</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" t="s">
+        <v>152</v>
+      </c>
+      <c r="E29">
+        <v>399</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30">
+        <v>399</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>156</v>
+      </c>
+      <c r="B31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" t="s">
+        <v>158</v>
+      </c>
+      <c r="E31">
+        <v>399</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>161</v>
+      </c>
+      <c r="E32">
+        <v>399</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>164</v>
+      </c>
+      <c r="E33">
+        <v>399</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>167</v>
+      </c>
+      <c r="E34">
+        <v>1199</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" t="s">
+        <v>170</v>
+      </c>
+      <c r="E35">
+        <v>1999</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" t="s">
+        <v>172</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36">
+        <v>3999</v>
+      </c>
+      <c r="F36">
         <v>0</v>
       </c>
     </row>
